--- a/Result/profitability/3221.xlsx
+++ b/Result/profitability/3221.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1612499999999999</v>
+        <v>0.2162499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>21.3525</v>
+        <v>22.185</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2487499999999999</v>
+        <v>0.2749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>22.0375</v>
+        <v>22.7875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2787499999999999</v>
+        <v>0.3174999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>21.97125</v>
+        <v>22.60375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2237499999999999</v>
+        <v>0.3149999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>21.6725</v>
+        <v>22.59625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22</v>
+        <v>0.29125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.3975</v>
+        <v>20.21875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2374999999999999</v>
+        <v>0.2575</v>
       </c>
       <c r="N7" t="n">
-        <v>18.66125</v>
+        <v>19.11125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.23375</v>
+        <v>0.24625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.4425</v>
+        <v>19.03625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3221</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>659</v>
+      </c>
+      <c r="D75" t="n">
+        <v>486</v>
+      </c>
+      <c r="E75" t="n">
+        <v>172</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>62</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.16625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2777777777777779</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2217553688141922</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.703703703703704</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.390000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3935037273695421</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
